--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/COLORADO_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/COLORADO_2019.xlsx
@@ -1741,7 +1741,7 @@
         <v>13</v>
       </c>
       <c r="D77">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="78">
@@ -1831,7 +1831,7 @@
         <v>13</v>
       </c>
       <c r="D82">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="83">
@@ -2767,7 +2767,7 @@
         <v>13</v>
       </c>
       <c r="D134">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="135">
@@ -2821,7 +2821,7 @@
         <v>13</v>
       </c>
       <c r="D137">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="138">
@@ -3109,7 +3109,7 @@
         <v>13</v>
       </c>
       <c r="D153">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="154">
@@ -3163,7 +3163,7 @@
         <v>13</v>
       </c>
       <c r="D156">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="157">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C190">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C305">
@@ -6637,7 +6637,7 @@
         <v>135</v>
       </c>
       <c r="D349">
-        <v>0.009682277845513877</v>
+        <v>0.009682277845513875</v>
       </c>
     </row>
     <row r="350">
@@ -6907,7 +6907,7 @@
         <v>13</v>
       </c>
       <c r="D364">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="365">
@@ -6943,7 +6943,7 @@
         <v>13</v>
       </c>
       <c r="D366">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="367">
@@ -7033,7 +7033,7 @@
         <v>13</v>
       </c>
       <c r="D371">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="372">
@@ -7069,7 +7069,7 @@
         <v>13</v>
       </c>
       <c r="D373">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="374">
@@ -7753,7 +7753,7 @@
         <v>13</v>
       </c>
       <c r="D411">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="412">
@@ -9625,7 +9625,7 @@
         <v>13</v>
       </c>
       <c r="D515">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="516">
@@ -9679,7 +9679,7 @@
         <v>13</v>
       </c>
       <c r="D518">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="519">
@@ -9733,7 +9733,7 @@
         <v>13</v>
       </c>
       <c r="D521">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="522">
@@ -11479,7 +11479,7 @@
         <v>13</v>
       </c>
       <c r="D618">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="619">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C757">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C763">
@@ -16645,7 +16645,7 @@
         <v>13</v>
       </c>
       <c r="D905">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="906">
@@ -16987,7 +16987,7 @@
         <v>13</v>
       </c>
       <c r="D924">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="925">
@@ -18265,7 +18265,7 @@
         <v>13</v>
       </c>
       <c r="D995">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="996">
@@ -21145,7 +21145,7 @@
         <v>13</v>
       </c>
       <c r="D1155">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="1156">
@@ -21703,7 +21703,7 @@
         <v>13</v>
       </c>
       <c r="D1186">
-        <v>0.0009323674962346697</v>
+        <v>0.0009323674962346696</v>
       </c>
     </row>
     <row r="1187">
